--- a/VerveStacks_NGA_grids_kan10/vt_vervestacks_NGA_v1.xlsx
+++ b/VerveStacks_NGA_grids_kan10/vt_vervestacks_NGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NGA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84300357-7322-41DA-8F57-4CF1826AA819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A03C6391-1A13-428B-A376-F75834247A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B445F13-AFCF-4F6E-9E72-7D59F21E5D01}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CF7DFDE8-DC15-4697-8A16-8A6CA89570D4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2542,7 +2542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A76392-752E-45A9-9299-21DAE6938E9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024F0BDC-62D6-4BAC-8324-05A1ABD797F5}">
   <dimension ref="B9:V112"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8946,7 +8946,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE30DE8-DC95-4CEA-895D-CFC0BA18BAD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCB8445-21EA-4A15-8105-48425348EF71}">
   <dimension ref="B9:W115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15263,7 +15263,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87DACDB0-EEC2-43EC-87E2-DCFD6A041514}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDE9CE3-CEBD-4A27-906E-DDC18D73782E}">
   <dimension ref="B9:W131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21794,7 +21794,7 @@
         <v>33</v>
       </c>
       <c r="N120">
-        <v>0.21311506666173191</v>
+        <v>0.21311506666173194</v>
       </c>
       <c r="P120" t="s">
         <v>171</v>
@@ -21847,7 +21847,7 @@
         <v>33</v>
       </c>
       <c r="N121">
-        <v>0.21311506666173191</v>
+        <v>0.21311506666173194</v>
       </c>
       <c r="P121" t="s">
         <v>171</v>
@@ -21900,7 +21900,7 @@
         <v>33</v>
       </c>
       <c r="N122">
-        <v>0.21311506666173191</v>
+        <v>0.21311506666173194</v>
       </c>
       <c r="P122" t="s">
         <v>171</v>
@@ -22449,7 +22449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65CDD9F-5C78-42B9-840B-203848B251BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE4DA27-DDCC-4F77-9F8F-3983D7A58B13}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
